--- a/public/men.xlsx
+++ b/public/men.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="-20" windowWidth="28860" windowHeight="6450"/>
+    <workbookView xWindow="-15" yWindow="-15" windowWidth="28860" windowHeight="6450"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -129,10 +129,10 @@
     </font>
     <font>
       <sz val="12"/>
-      <color indexed="0"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -495,9 +495,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="15.5"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="7" width="20.83203125" customWidth="1"/>
+    <col min="1" max="7" width="20.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -634,5 +634,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>